--- a/data/trans_bre/KIDM_C_3_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_C_3_R-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 3,54</t>
+          <t>-11,11; 3,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 8,01</t>
+          <t>-16,88; 7,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 0,05</t>
+          <t>-27,9; -1,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 0,0</t>
+          <t>-8,78; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-78,83; 160,54</t>
+          <t>-78,86; 138,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-91,59; 18,64</t>
+          <t>-91,94; 5,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 12,2</t>
+          <t>-4,41; 10,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 19,27</t>
+          <t>-8,3; 18,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 22,2</t>
+          <t>2,39; 22,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 8,78</t>
+          <t>-5,74; 8,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,7; 232,85</t>
+          <t>-47,64; 273,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,74; —</t>
+          <t>4,75; 1413,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 9,39</t>
+          <t>-5,44; 10,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 17,62</t>
+          <t>-8,77; 17,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,3; -0,68</t>
+          <t>-19,41; -1,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,54</t>
+          <t>0,0; 24,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-56,15; 356,84</t>
+          <t>-53,22; 387,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 170,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 9,48</t>
+          <t>-1,49; 9,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 21,13</t>
+          <t>2,93; 20,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 6,66</t>
+          <t>-5,49; 6,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 10,45</t>
+          <t>-4,6; 10,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,84; 931,48</t>
+          <t>-45,54; 820,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 296,9</t>
+          <t>18,99; 282,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-53,29; 182,65</t>
+          <t>-57,03; 164,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 7,3</t>
+          <t>-7,54; 7,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 10,63</t>
+          <t>-7,01; 9,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 4,26</t>
+          <t>-14,94; 4,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 16,73</t>
+          <t>-1,14; 15,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-77,03; 226,79</t>
+          <t>-77,72; 231,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,2; 166,54</t>
+          <t>-49,45; 139,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-73,2; 52,65</t>
+          <t>-72,32; 68,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,31</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 14,48</t>
+          <t>-8,31; 12,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 13,77</t>
+          <t>-7,55; 12,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,73</t>
+          <t>-1,55; 3,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,09; 9,31</t>
+          <t>0,03; 9,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 1,89</t>
+          <t>-5,76; 2,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 5,02</t>
+          <t>-0,4; 5,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-36,6; 138,19</t>
+          <t>-32,57; 164,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 103,38</t>
+          <t>0,16; 100,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-46,8; 25,56</t>
+          <t>-44,33; 26,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-36,18; 561,19</t>
+          <t>-31,11; 620,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/KIDM_C_3_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/KIDM_C_3_R-Clase-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 3,28</t>
+          <t>-10,82; 3,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 7,97</t>
+          <t>-17,44; 7,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,9; -1,16</t>
+          <t>-27,02; -0,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 0,0</t>
+          <t>-8,28; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-78,86; 138,46</t>
+          <t>-84,49; 125,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-91,94; 5,38</t>
+          <t>-90,22; 18,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 10,56</t>
+          <t>-4,45; 10,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 18,81</t>
+          <t>-9,6; 18,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 22,36</t>
+          <t>2,24; 22,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 8,87</t>
+          <t>-5,86; 9,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,64; 273,07</t>
+          <t>-50,58; 225,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,75; 1413,96</t>
+          <t>-1,27; 1456,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 10,63</t>
+          <t>-5,54; 10,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 17,11</t>
+          <t>-9,21; 16,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-19,41; -1,35</t>
+          <t>-19,65; -0,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,52</t>
+          <t>0,0; 25,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,22; 387,6</t>
+          <t>-53,3; 358,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 159,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 9,32</t>
+          <t>-1,6; 9,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 20,08</t>
+          <t>2,33; 20,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 6,02</t>
+          <t>-6,22; 5,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 10,51</t>
+          <t>-3,86; 11,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-45,54; 820,29</t>
+          <t>-45,47; 641,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,99; 282,12</t>
+          <t>9,72; 320,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-57,03; 164,65</t>
+          <t>-61,68; 148,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,37 +1060,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 7,41</t>
+          <t>-7,72; 7,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 9,66</t>
+          <t>-7,17; 10,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 4,18</t>
+          <t>-14,87; 3,74</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 15,67</t>
+          <t>-1,59; 14,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-77,72; 231,64</t>
+          <t>-77,67; 278,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-49,45; 139,28</t>
+          <t>-48,22; 134,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-72,32; 68,85</t>
+          <t>-72,27; 52,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,8</t>
+          <t>0,0; 11,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 12,89</t>
+          <t>-8,41; 13,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 12,95</t>
+          <t>-6,77; 14,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 3,85</t>
+          <t>-1,5; 3,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,03; 9,07</t>
+          <t>0,04; 9,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 2,2</t>
+          <t>-5,27; 2,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 5,18</t>
+          <t>-0,83; 5,2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-32,57; 164,91</t>
+          <t>-31,08; 150,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 100,28</t>
+          <t>0,48; 101,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-44,33; 26,57</t>
+          <t>-43,54; 27,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 620,36</t>
+          <t>-37,39; 597,81</t>
         </is>
       </c>
     </row>
